--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PAR-Close-Operation-Input.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PAR-Close-Operation-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5505" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5485" uniqueCount="400">
   <si>
     <t>Property</t>
   </si>
@@ -383,10 +383,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -427,6 +423,402 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.name</t>
+  </si>
+  <si>
+    <t>Name from the definition</t>
+  </si>
+  <si>
+    <t>The name of the parameter (reference to the operation definition).</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>If parameter is a data type</t>
+  </si>
+  <si>
+    <t>If the parameter is a data type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inv-1
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part</t>
+  </si>
+  <si>
+    <t>Named part of a multi-part parameter</t>
+  </si>
+  <si>
+    <t>A named part of a multi-part parameter.</t>
+  </si>
+  <si>
+    <t>Only one level of nested parameters is allowed.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation</t>
+  </si>
+  <si>
+    <t>rxDispensation</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}erp-eu-parameters-close-dispense-medication-references:If a reference from a MedicationDispense to a Medication exists, the reference must resolve to the Medication. {part.where(name = 'medicationDispense').resource.medication.ofType(Reference).reference.exists() implies ((part.where(name = 'medicationDispense').resource.medication.reference.split('/').last().split(':').last()) = (part.where(name = 'medication').resource.id))}</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense</t>
+  </si>
+  <si>
+    <t>medicationDispense</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MedicationDispense {https://gematik.de/fhir/tiflow/xborder/StructureDefinition/GEM-ERPEU-PR-MedicationDispense}
+</t>
+  </si>
+  <si>
+    <t>Dispensing a medication to a named patient</t>
+  </si>
+  <si>
+    <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>
+  </si>
+  <si>
+    <t>Supply[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medicationDispense.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication</t>
+  </si>
+  <si>
+    <t>medication</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication {https://gematik.de/fhir/tiflow/xborder/StructureDefinition/GEM-ERPEU-PR-Medication}
+</t>
+  </si>
+  <si>
+    <t>Definition of a Medication</t>
+  </si>
+  <si>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct[classCode=ADMM]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:rxDispensation.part:medication.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData</t>
+  </si>
+  <si>
+    <t>requestData</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr</t>
+  </si>
+  <si>
+    <t>kvnr</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:kvnr.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode</t>
+  </si>
+  <si>
+    <t>accessCode</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/tiflow/xborder/StructureDefinition/GEM-ERPEU-PR-AccessCode}
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:accessCode.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode</t>
+  </si>
+  <si>
+    <t>countryCode</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.value[x].id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.value[x].id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:countryCode.value[x].extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.value[x].extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -435,412 +827,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.name</t>
-  </si>
-  <si>
-    <t>Name from the definition</t>
-  </si>
-  <si>
-    <t>The name of the parameter (reference to the operation definition).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>If parameter is a data type</t>
-  </si>
-  <si>
-    <t>If the parameter is a data type.</t>
-  </si>
-  <si>
-    <t>ele-1
-inv-1</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part</t>
-  </si>
-  <si>
-    <t>Named part of a multi-part parameter</t>
-  </si>
-  <si>
-    <t>A named part of a multi-part parameter.</t>
-  </si>
-  <si>
-    <t>Only one level of nested parameters is allowed.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation</t>
-  </si>
-  <si>
-    <t>rxDispensation</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}erp-eu-parameters-close-dispense-medication-references:If a reference from a MedicationDispense to a Medication exists, the reference must resolve to the Medication. {part.where(name = 'medicationDispense').resource.medication.ofType(Reference).reference.exists() implies ((part.where(name = 'medicationDispense').resource.medication.reference.split('/').last().split(':').last()) = (part.where(name = 'medication').resource.id))}</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense</t>
-  </si>
-  <si>
-    <t>medicationDispense</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MedicationDispense {https://gematik.de/fhir/tiflow/xborder/StructureDefinition/GEM-ERPEU-PR-MedicationDispense}
-</t>
-  </si>
-  <si>
-    <t>Dispensing a medication to a named patient</t>
-  </si>
-  <si>
-    <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>
-  </si>
-  <si>
-    <t>Supply[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medicationDispense.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication</t>
-  </si>
-  <si>
-    <t>medication</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medication {https://gematik.de/fhir/tiflow/xborder/StructureDefinition/GEM-ERPEU-PR-Medication}
-</t>
-  </si>
-  <si>
-    <t>Definition of a Medication</t>
-  </si>
-  <si>
-    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct[classCode=ADMM]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:rxDispensation.part:medication.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData</t>
-  </si>
-  <si>
-    <t>requestData</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr</t>
-  </si>
-  <si>
-    <t>kvnr</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
-</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:kvnr.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode</t>
-  </si>
-  <si>
-    <t>accessCode</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/tiflow/xborder/StructureDefinition/GEM-ERPEU-PR-AccessCode}
-</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:accessCode.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode</t>
-  </si>
-  <si>
-    <t>countryCode</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.value[x].id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.value[x].id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:countryCode.value[x].extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.value[x].extension</t>
   </si>
   <si>
     <t>Parameters.parameter:requestData.part:countryCode.value[x].system</t>
@@ -2363,24 +2349,24 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2403,13 +2389,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2460,7 +2446,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2483,14 +2469,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2509,16 +2495,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2556,19 +2542,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2580,7 +2566,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2591,14 +2577,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2617,19 +2603,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2678,7 +2664,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2690,21 +2676,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2727,17 +2713,15 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2786,7 +2770,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2809,10 +2793,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2835,13 +2819,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2892,7 +2876,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2901,7 +2885,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2910,15 +2894,15 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2941,16 +2925,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3000,7 +2984,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3009,7 +2993,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -3018,15 +3002,15 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3052,13 +3036,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3108,7 +3092,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3120,7 +3104,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
@@ -3131,13 +3115,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -3225,24 +3209,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3265,13 +3249,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3322,7 +3306,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3345,14 +3329,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3371,16 +3355,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3418,19 +3402,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3442,7 +3426,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -3453,14 +3437,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3479,19 +3463,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3540,7 +3524,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3552,21 +3536,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3589,17 +3573,15 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3609,7 +3591,7 @@
         <v>75</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>75</v>
@@ -3648,7 +3630,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3671,10 +3653,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3697,13 +3679,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3754,7 +3736,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3763,7 +3745,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3772,15 +3754,15 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3803,16 +3785,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3862,7 +3844,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3871,7 +3853,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3880,15 +3862,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3896,7 +3878,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>77</v>
@@ -3914,13 +3896,13 @@
         <v>75</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3968,7 +3950,7 @@
         <v>118</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3980,7 +3962,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>75</v>
@@ -3991,10 +3973,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4017,13 +3999,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4074,7 +4056,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4097,14 +4079,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4123,16 +4105,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4170,19 +4152,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4194,7 +4176,7 @@
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
@@ -4205,14 +4187,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4231,19 +4213,19 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4292,7 +4274,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4304,21 +4286,21 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4341,17 +4323,15 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4400,7 +4380,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -4423,10 +4403,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4449,13 +4429,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4506,7 +4486,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4515,7 +4495,7 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>96</v>
@@ -4524,15 +4504,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4555,16 +4535,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4614,7 +4594,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4623,7 +4603,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>75</v>
@@ -4632,15 +4612,15 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4666,13 +4646,13 @@
         <v>75</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4722,7 +4702,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4734,7 +4714,7 @@
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
@@ -4745,13 +4725,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -4776,13 +4756,13 @@
         <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4832,7 +4812,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4844,7 +4824,7 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
@@ -4855,10 +4835,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4881,13 +4861,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4938,7 +4918,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4961,14 +4941,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4987,16 +4967,16 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5034,19 +5014,19 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5058,7 +5038,7 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
@@ -5069,14 +5049,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5095,19 +5075,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5156,7 +5136,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5168,21 +5148,21 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5205,17 +5185,15 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5225,7 +5203,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5264,7 +5242,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -5287,10 +5265,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5313,13 +5291,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5370,7 +5348,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5379,7 +5357,7 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>96</v>
@@ -5388,15 +5366,15 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5419,16 +5397,16 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5478,7 +5456,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5496,15 +5474,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5530,13 +5508,13 @@
         <v>75</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5586,7 +5564,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5598,7 +5576,7 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
@@ -5609,13 +5587,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
@@ -5640,13 +5618,13 @@
         <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5696,7 +5674,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5708,7 +5686,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5719,10 +5697,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5745,13 +5723,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5802,7 +5780,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5825,14 +5803,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5851,16 +5829,16 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5898,19 +5876,19 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5922,7 +5900,7 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
@@ -5933,14 +5911,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5959,19 +5937,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -6020,7 +5998,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6032,21 +6010,21 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6069,17 +6047,15 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6089,7 +6065,7 @@
         <v>75</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>75</v>
@@ -6128,7 +6104,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -6151,10 +6127,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6177,13 +6153,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6234,7 +6210,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6243,7 +6219,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>96</v>
@@ -6252,15 +6228,15 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6283,16 +6259,16 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6342,7 +6318,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6360,15 +6336,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6394,13 +6370,13 @@
         <v>75</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6450,7 +6426,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6462,7 +6438,7 @@
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6473,13 +6449,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>75</v>
@@ -6567,24 +6543,24 @@
         <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6607,13 +6583,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6664,7 +6640,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6687,14 +6663,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6713,16 +6689,16 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6760,19 +6736,19 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6784,7 +6760,7 @@
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
@@ -6795,14 +6771,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6821,19 +6797,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6882,7 +6858,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6894,21 +6870,21 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6931,17 +6907,15 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6951,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>75</v>
@@ -6990,7 +6964,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -7013,10 +6987,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7039,13 +7013,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7096,7 +7070,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7105,7 +7079,7 @@
         <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>96</v>
@@ -7114,15 +7088,15 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7145,16 +7119,16 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7204,7 +7178,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7213,7 +7187,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>75</v>
@@ -7222,15 +7196,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7238,7 +7212,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>77</v>
@@ -7256,13 +7230,13 @@
         <v>75</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7310,7 +7284,7 @@
         <v>118</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7322,7 +7296,7 @@
         <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
@@ -7333,10 +7307,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7359,13 +7333,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7416,7 +7390,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7439,14 +7413,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7465,16 +7439,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7512,19 +7486,19 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7536,7 +7510,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7547,14 +7521,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7573,19 +7547,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7634,7 +7608,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7646,21 +7620,21 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7683,17 +7657,15 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7742,7 +7714,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -7765,10 +7737,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7791,13 +7763,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7848,7 +7820,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7857,7 +7829,7 @@
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>96</v>
@@ -7866,15 +7838,15 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7897,16 +7869,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7956,7 +7928,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7965,7 +7937,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>75</v>
@@ -7974,15 +7946,15 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8008,13 +7980,13 @@
         <v>75</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8064,7 +8036,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8076,7 +8048,7 @@
         <v>75</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
@@ -8087,13 +8059,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>75</v>
@@ -8118,13 +8090,13 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8174,7 +8146,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8186,7 +8158,7 @@
         <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -8197,10 +8169,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8223,13 +8195,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8280,7 +8252,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8303,14 +8275,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8329,16 +8301,16 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8376,19 +8348,19 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8400,7 +8372,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -8411,14 +8383,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8437,19 +8409,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -8498,7 +8470,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8510,21 +8482,21 @@
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8547,17 +8519,15 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8567,7 +8537,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -8606,7 +8576,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -8629,10 +8599,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8655,13 +8625,13 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8712,7 +8682,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8721,7 +8691,7 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>96</v>
@@ -8730,15 +8700,15 @@
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8761,16 +8731,16 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8820,7 +8790,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -8829,7 +8799,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>75</v>
@@ -8838,15 +8808,15 @@
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8872,13 +8842,13 @@
         <v>75</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8928,7 +8898,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8940,7 +8910,7 @@
         <v>75</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>75</v>
@@ -8951,13 +8921,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>75</v>
@@ -8982,13 +8952,13 @@
         <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9038,7 +9008,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9050,7 +9020,7 @@
         <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
@@ -9061,10 +9031,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9087,13 +9057,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9144,7 +9114,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9167,14 +9137,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9193,16 +9163,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9240,19 +9210,19 @@
         <v>75</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9264,7 +9234,7 @@
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -9275,14 +9245,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9301,19 +9271,19 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -9362,7 +9332,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9374,21 +9344,21 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9411,17 +9381,15 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9431,7 +9399,7 @@
         <v>75</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>75</v>
@@ -9470,7 +9438,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>84</v>
@@ -9493,10 +9461,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9519,13 +9487,13 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9576,7 +9544,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -9585,7 +9553,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -9594,15 +9562,15 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9625,16 +9593,16 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9684,7 +9652,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9693,7 +9661,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>75</v>
@@ -9702,15 +9670,15 @@
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9736,13 +9704,13 @@
         <v>75</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9792,7 +9760,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9804,7 +9772,7 @@
         <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
@@ -9815,13 +9783,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
@@ -9846,13 +9814,13 @@
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9902,7 +9870,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9914,7 +9882,7 @@
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -9925,10 +9893,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9951,13 +9919,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10008,7 +9976,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10031,14 +9999,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10057,16 +10025,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10104,19 +10072,19 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10128,7 +10096,7 @@
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -10139,14 +10107,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10165,19 +10133,19 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10226,7 +10194,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10238,21 +10206,21 @@
         <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10275,17 +10243,15 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10295,7 +10261,7 @@
         <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>75</v>
@@ -10334,7 +10300,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>84</v>
@@ -10357,10 +10323,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10383,13 +10349,13 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10416,11 +10382,11 @@
         <v>75</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -10438,7 +10404,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10447,7 +10413,7 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>96</v>
@@ -10456,15 +10422,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10487,13 +10453,13 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10544,7 +10510,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10567,14 +10533,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10593,16 +10559,16 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10640,19 +10606,19 @@
         <v>75</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10664,7 +10630,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -10675,10 +10641,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10704,16 +10670,16 @@
         <v>98</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -10723,7 +10689,7 @@
         <v>75</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>75</v>
@@ -10762,7 +10728,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10777,18 +10743,18 @@
         <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10811,16 +10777,16 @@
         <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10870,7 +10836,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10885,18 +10851,18 @@
         <v>96</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10922,14 +10888,14 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -10978,7 +10944,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -10993,18 +10959,18 @@
         <v>96</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11027,19 +10993,17 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11088,7 +11052,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -11103,18 +11067,18 @@
         <v>96</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11137,19 +11101,19 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O89" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11198,7 +11162,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11213,18 +11177,18 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11247,16 +11211,16 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11306,7 +11270,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11315,7 +11279,7 @@
         <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>75</v>
@@ -11324,15 +11288,15 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11358,13 +11322,13 @@
         <v>78</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11414,7 +11378,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11426,7 +11390,7 @@
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
@@ -11437,13 +11401,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>75</v>
@@ -11468,13 +11432,13 @@
         <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11524,7 +11488,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11536,7 +11500,7 @@
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
@@ -11547,10 +11511,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11573,13 +11537,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11630,7 +11594,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11653,14 +11617,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11679,16 +11643,16 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11726,19 +11690,19 @@
         <v>75</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11750,7 +11714,7 @@
         <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
@@ -11761,14 +11725,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -11787,19 +11751,19 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11848,7 +11812,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -11860,21 +11824,21 @@
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11897,17 +11861,15 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
@@ -11917,7 +11879,7 @@
         <v>75</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>75</v>
@@ -11956,7 +11918,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>84</v>
@@ -11979,10 +11941,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12005,13 +11967,13 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12062,7 +12024,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12071,7 +12033,7 @@
         <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>96</v>
@@ -12080,15 +12042,15 @@
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12111,16 +12073,16 @@
         <v>85</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12170,7 +12132,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12179,7 +12141,7 @@
         <v>84</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>75</v>
@@ -12188,15 +12150,15 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12222,13 +12184,13 @@
         <v>75</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12278,7 +12240,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12290,7 +12252,7 @@
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -12301,13 +12263,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
@@ -12332,13 +12294,13 @@
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12388,7 +12350,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12400,7 +12362,7 @@
         <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -12411,10 +12373,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12437,13 +12399,13 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12494,7 +12456,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12517,14 +12479,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -12543,16 +12505,16 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12590,19 +12552,19 @@
         <v>75</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -12614,7 +12576,7 @@
         <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -12625,14 +12587,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -12651,19 +12613,19 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12712,7 +12674,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12724,21 +12686,21 @@
         <v>75</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12761,17 +12723,15 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -12781,7 +12741,7 @@
         <v>75</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>75</v>
@@ -12820,7 +12780,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>84</v>
@@ -12843,10 +12803,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12869,13 +12829,13 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12902,11 +12862,11 @@
         <v>75</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>75</v>
@@ -12924,7 +12884,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -12933,7 +12893,7 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>96</v>
@@ -12942,15 +12902,15 @@
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12973,13 +12933,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13030,7 +12990,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13053,14 +13013,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13079,16 +13039,16 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13126,19 +13086,19 @@
         <v>75</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13150,7 +13110,7 @@
         <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -13161,10 +13121,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13190,16 +13150,16 @@
         <v>98</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -13248,7 +13208,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13263,18 +13223,18 @@
         <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13297,16 +13257,16 @@
         <v>85</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -13356,7 +13316,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -13371,18 +13331,18 @@
         <v>96</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13408,14 +13368,14 @@
         <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -13464,7 +13424,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13479,18 +13439,18 @@
         <v>96</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13513,19 +13473,17 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13574,7 +13532,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -13589,18 +13547,18 @@
         <v>96</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13623,19 +13581,19 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O112" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -13684,7 +13642,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -13699,18 +13657,18 @@
         <v>96</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13733,16 +13691,16 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13792,7 +13750,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13801,7 +13759,7 @@
         <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>75</v>
@@ -13810,15 +13768,15 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13844,13 +13802,13 @@
         <v>75</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13900,7 +13858,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13912,7 +13870,7 @@
         <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -13923,13 +13881,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>75</v>
@@ -13954,13 +13912,13 @@
         <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14010,7 +13968,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14022,7 +13980,7 @@
         <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
@@ -14033,10 +13991,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14059,13 +14017,13 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14116,7 +14074,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14139,14 +14097,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -14165,16 +14123,16 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -14212,19 +14170,19 @@
         <v>75</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14236,7 +14194,7 @@
         <v>75</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
@@ -14247,14 +14205,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -14273,19 +14231,19 @@
         <v>85</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -14334,7 +14292,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14346,21 +14304,21 @@
         <v>75</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14383,17 +14341,15 @@
         <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -14403,7 +14359,7 @@
         <v>75</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>75</v>
@@ -14442,7 +14398,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>84</v>
@@ -14465,10 +14421,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14491,13 +14447,13 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14548,7 +14504,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -14557,7 +14513,7 @@
         <v>84</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>96</v>
@@ -14566,15 +14522,15 @@
         <v>75</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14597,16 +14553,16 @@
         <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14656,7 +14612,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -14665,7 +14621,7 @@
         <v>84</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>75</v>
@@ -14674,15 +14630,15 @@
         <v>75</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14708,13 +14664,13 @@
         <v>75</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14764,7 +14720,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14776,7 +14732,7 @@
         <v>75</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>75</v>
@@ -14787,13 +14743,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>75</v>
@@ -14818,13 +14774,13 @@
         <v>114</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14874,7 +14830,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -14886,7 +14842,7 @@
         <v>75</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
@@ -14897,10 +14853,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14923,13 +14879,13 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14980,7 +14936,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15003,14 +14959,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -15029,16 +14985,16 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15076,19 +15032,19 @@
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15100,7 +15056,7 @@
         <v>75</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
@@ -15111,14 +15067,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -15137,19 +15093,19 @@
         <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>75</v>
@@ -15198,7 +15154,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -15210,21 +15166,21 @@
         <v>75</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15247,17 +15203,15 @@
         <v>85</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
@@ -15267,7 +15221,7 @@
         <v>75</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>75</v>
@@ -15306,7 +15260,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>84</v>
@@ -15329,10 +15283,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15355,13 +15309,13 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15388,11 +15342,11 @@
         <v>75</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>75</v>
@@ -15410,7 +15364,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -15419,7 +15373,7 @@
         <v>84</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>96</v>
@@ -15428,15 +15382,15 @@
         <v>75</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15459,13 +15413,13 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15516,7 +15470,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -15539,14 +15493,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -15565,16 +15519,16 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -15612,19 +15566,19 @@
         <v>75</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -15636,7 +15590,7 @@
         <v>75</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>75</v>
@@ -15647,10 +15601,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15676,16 +15630,16 @@
         <v>98</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>75</v>
@@ -15734,7 +15688,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -15749,18 +15703,18 @@
         <v>96</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15783,16 +15737,16 @@
         <v>85</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15842,7 +15796,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -15857,18 +15811,18 @@
         <v>96</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15894,14 +15848,14 @@
         <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>75</v>
@@ -15950,7 +15904,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -15965,18 +15919,18 @@
         <v>96</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15999,19 +15953,17 @@
         <v>85</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -16060,7 +16012,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16075,18 +16027,18 @@
         <v>96</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16109,19 +16061,19 @@
         <v>85</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O135" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
@@ -16170,7 +16122,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -16185,18 +16137,18 @@
         <v>96</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16219,16 +16171,16 @@
         <v>85</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -16278,7 +16230,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -16287,7 +16239,7 @@
         <v>84</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>75</v>
@@ -16296,15 +16248,15 @@
         <v>75</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16330,13 +16282,13 @@
         <v>75</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -16386,7 +16338,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -16398,7 +16350,7 @@
         <v>75</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>75</v>
@@ -16409,13 +16361,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>75</v>
@@ -16503,24 +16455,24 @@
         <v>77</v>
       </c>
       <c r="AI138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ138" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16543,13 +16495,13 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -16600,7 +16552,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -16623,14 +16575,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -16649,16 +16601,16 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -16696,19 +16648,19 @@
         <v>75</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -16720,7 +16672,7 @@
         <v>75</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>75</v>
@@ -16731,14 +16683,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -16757,19 +16709,19 @@
         <v>85</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>75</v>
@@ -16818,7 +16770,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -16830,21 +16782,21 @@
         <v>75</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16867,17 +16819,15 @@
         <v>85</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>75</v>
@@ -16887,7 +16837,7 @@
         <v>75</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>75</v>
@@ -16926,7 +16876,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>84</v>
@@ -16949,10 +16899,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16975,13 +16925,13 @@
         <v>85</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -17032,7 +16982,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -17041,7 +16991,7 @@
         <v>84</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>96</v>
@@ -17050,15 +17000,15 @@
         <v>75</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17081,16 +17031,16 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17140,7 +17090,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -17155,18 +17105,18 @@
         <v>75</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17192,13 +17142,13 @@
         <v>75</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -17248,7 +17198,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -17260,7 +17210,7 @@
         <v>75</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>75</v>
@@ -17271,13 +17221,13 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>75</v>
@@ -17365,24 +17315,24 @@
         <v>77</v>
       </c>
       <c r="AI146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ146" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK146" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17405,13 +17355,13 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -17462,7 +17412,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -17485,14 +17435,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -17511,16 +17461,16 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -17558,19 +17508,19 @@
         <v>75</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -17582,7 +17532,7 @@
         <v>75</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>75</v>
@@ -17593,14 +17543,14 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -17619,19 +17569,19 @@
         <v>85</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>75</v>
@@ -17680,7 +17630,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -17692,21 +17642,21 @@
         <v>75</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17729,17 +17679,15 @@
         <v>85</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>75</v>
@@ -17749,7 +17697,7 @@
         <v>75</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>75</v>
@@ -17788,7 +17736,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>84</v>
@@ -17811,10 +17759,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17837,13 +17785,13 @@
         <v>85</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17894,7 +17842,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -17903,7 +17851,7 @@
         <v>84</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>96</v>
@@ -17912,15 +17860,15 @@
         <v>75</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17943,16 +17891,16 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18002,7 +17950,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
@@ -18017,18 +17965,18 @@
         <v>75</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18054,13 +18002,13 @@
         <v>75</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18110,7 +18058,7 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -18122,7 +18070,7 @@
         <v>75</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>75</v>
@@ -18133,13 +18081,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>75</v>
@@ -18227,24 +18175,24 @@
         <v>77</v>
       </c>
       <c r="AI154" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ154" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18267,13 +18215,13 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -18324,7 +18272,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -18347,14 +18295,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -18373,16 +18321,16 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -18420,19 +18368,19 @@
         <v>75</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -18444,7 +18392,7 @@
         <v>75</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>75</v>
@@ -18455,14 +18403,14 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -18481,19 +18429,19 @@
         <v>85</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>75</v>
@@ -18542,7 +18490,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -18554,21 +18502,21 @@
         <v>75</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18591,17 +18539,15 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>75</v>
@@ -18611,7 +18557,7 @@
         <v>75</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>75</v>
@@ -18650,7 +18596,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -18673,10 +18619,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18699,13 +18645,13 @@
         <v>85</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -18756,7 +18702,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -18765,7 +18711,7 @@
         <v>84</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>96</v>
@@ -18774,15 +18720,15 @@
         <v>75</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18805,16 +18751,16 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -18864,7 +18810,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -18879,18 +18825,18 @@
         <v>75</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18916,13 +18862,13 @@
         <v>75</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -18972,7 +18918,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -18984,7 +18930,7 @@
         <v>75</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>75</v>
